--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/185.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/185.xlsx
@@ -426,13 +426,13 @@
         <v>-5.149346409129084</v>
       </c>
       <c r="E2">
-        <v>-16.19346285021619</v>
+        <v>-13.10071888430768</v>
       </c>
       <c r="F2">
-        <v>0.7768744139951258</v>
+        <v>-0.1990305103933088</v>
       </c>
       <c r="G2">
-        <v>-11.40358576833481</v>
+        <v>-11.51195647656285</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.057062858752157</v>
       </c>
       <c r="E3">
-        <v>-15.83713987292264</v>
+        <v>-13.45480932391544</v>
       </c>
       <c r="F3">
-        <v>0.8963095956079917</v>
+        <v>-0.1751775237479175</v>
       </c>
       <c r="G3">
-        <v>-11.38129586521889</v>
+        <v>-10.54004320659807</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.925149130780304</v>
       </c>
       <c r="E4">
-        <v>-17.51424210776733</v>
+        <v>-13.54649733714874</v>
       </c>
       <c r="F4">
-        <v>0.8155342590969181</v>
+        <v>0.1811127553132836</v>
       </c>
       <c r="G4">
-        <v>-11.49288773425665</v>
+        <v>-9.553523809714036</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.754154127215652</v>
       </c>
       <c r="E5">
-        <v>-16.90421137419406</v>
+        <v>-14.23176866635946</v>
       </c>
       <c r="F5">
-        <v>1.009506559619942</v>
+        <v>0.2971952315031642</v>
       </c>
       <c r="G5">
-        <v>-10.25756097682314</v>
+        <v>-10.27251471102403</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.535563332393445</v>
       </c>
       <c r="E6">
-        <v>-18.5762688889942</v>
+        <v>-16.29867288683639</v>
       </c>
       <c r="F6">
-        <v>1.003726033028588</v>
+        <v>-0.3313103388333463</v>
       </c>
       <c r="G6">
-        <v>-9.990886601998232</v>
+        <v>-9.509751776593793</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.273929380870444</v>
       </c>
       <c r="E7">
-        <v>-18.36816739444571</v>
+        <v>-17.1203780809502</v>
       </c>
       <c r="F7">
-        <v>1.288341741621788</v>
+        <v>-0.0224322556156137</v>
       </c>
       <c r="G7">
-        <v>-9.23958477622495</v>
+        <v>-9.1405200115078</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.970131012835304</v>
       </c>
       <c r="E8">
-        <v>-19.66082935688323</v>
+        <v>-17.46694672523122</v>
       </c>
       <c r="F8">
-        <v>1.30207880673231</v>
+        <v>0.2051249044031765</v>
       </c>
       <c r="G8">
-        <v>-9.164835968493746</v>
+        <v>-9.425610951167677</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.641108174496067</v>
       </c>
       <c r="E9">
-        <v>-20.11042531331276</v>
+        <v>-16.66399394198318</v>
       </c>
       <c r="F9">
-        <v>1.471381720210533</v>
+        <v>0.3141781018873791</v>
       </c>
       <c r="G9">
-        <v>-9.04053160458519</v>
+        <v>-8.312893558326619</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.299134639150423</v>
       </c>
       <c r="E10">
-        <v>-20.51868535900028</v>
+        <v>-18.33596088730316</v>
       </c>
       <c r="F10">
-        <v>1.737808566364911</v>
+        <v>0.8963998668451717</v>
       </c>
       <c r="G10">
-        <v>-8.218854201738083</v>
+        <v>-8.06237795627889</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.963970316195468</v>
       </c>
       <c r="E11">
-        <v>-22.29219427699426</v>
+        <v>-19.62147238928257</v>
       </c>
       <c r="F11">
-        <v>1.761359857033411</v>
+        <v>0.8767999224356932</v>
       </c>
       <c r="G11">
-        <v>-7.951898430542332</v>
+        <v>-7.513453089866796</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.652652058493465</v>
       </c>
       <c r="E12">
-        <v>-21.63144010606107</v>
+        <v>-20.03549265390784</v>
       </c>
       <c r="F12">
-        <v>2.001782252056274</v>
+        <v>0.7230394988115927</v>
       </c>
       <c r="G12">
-        <v>-7.367560658496654</v>
+        <v>-7.190131970319414</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.37416379792864</v>
       </c>
       <c r="E13">
-        <v>-22.43672505342306</v>
+        <v>-20.76498453180346</v>
       </c>
       <c r="F13">
-        <v>2.171180187889423</v>
+        <v>1.100384356165603</v>
       </c>
       <c r="G13">
-        <v>-6.169408016923626</v>
+        <v>-6.682794176971645</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.138897863667075</v>
       </c>
       <c r="E14">
-        <v>-24.43208844152682</v>
+        <v>-22.33972514017876</v>
       </c>
       <c r="F14">
-        <v>2.212822151229988</v>
+        <v>1.575562646445886</v>
       </c>
       <c r="G14">
-        <v>-6.849112674319089</v>
+        <v>-6.11269837183591</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.941158735395616</v>
       </c>
       <c r="E15">
-        <v>-24.77655587386828</v>
+        <v>-22.85053700824398</v>
       </c>
       <c r="F15">
-        <v>2.922936879242051</v>
+        <v>1.43012459740742</v>
       </c>
       <c r="G15">
-        <v>-6.49076267242068</v>
+        <v>-5.480463626928056</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.777438176657863</v>
       </c>
       <c r="E16">
-        <v>-25.57222687091199</v>
+        <v>-23.13897363168854</v>
       </c>
       <c r="F16">
-        <v>3.359391976183924</v>
+        <v>2.409683131342773</v>
       </c>
       <c r="G16">
-        <v>-6.524281946005801</v>
+        <v>-5.423952614572697</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.638068128930662</v>
       </c>
       <c r="E17">
-        <v>-27.12706030754958</v>
+        <v>-24.53896495658185</v>
       </c>
       <c r="F17">
-        <v>3.194878189393989</v>
+        <v>1.955688491387409</v>
       </c>
       <c r="G17">
-        <v>-6.086700657716014</v>
+        <v>-5.67504094099872</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.518533144015492</v>
       </c>
       <c r="E18">
-        <v>-28.00263169998463</v>
+        <v>-24.84544754894697</v>
       </c>
       <c r="F18">
-        <v>3.477544356005284</v>
+        <v>2.43046452036517</v>
       </c>
       <c r="G18">
-        <v>-5.853131738283814</v>
+        <v>-6.024478954305412</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.422356157014921</v>
       </c>
       <c r="E19">
-        <v>-29.36140485446013</v>
+        <v>-26.56819227331497</v>
       </c>
       <c r="F19">
-        <v>3.669188608832612</v>
+        <v>2.6548408070528</v>
       </c>
       <c r="G19">
-        <v>-5.014471236820244</v>
+        <v>-5.47417690094898</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.353594740435579</v>
       </c>
       <c r="E20">
-        <v>-29.75103022960608</v>
+        <v>-27.06528739361095</v>
       </c>
       <c r="F20">
-        <v>4.064891785158396</v>
+        <v>2.933390921989867</v>
       </c>
       <c r="G20">
-        <v>-5.406012768295386</v>
+        <v>-4.106236310303351</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.326486226842929</v>
       </c>
       <c r="E21">
-        <v>-29.50824515263285</v>
+        <v>-25.92960498264932</v>
       </c>
       <c r="F21">
-        <v>4.298415557213604</v>
+        <v>2.883691062951546</v>
       </c>
       <c r="G21">
-        <v>-5.895377609910454</v>
+        <v>-5.399063933208456</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.346692760159125</v>
       </c>
       <c r="E22">
-        <v>-30.73354606420627</v>
+        <v>-27.8082560101534</v>
       </c>
       <c r="F22">
-        <v>4.112521740565238</v>
+        <v>3.115488595558925</v>
       </c>
       <c r="G22">
-        <v>-5.441948740124175</v>
+        <v>-4.17137460433405</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.423379259950706</v>
       </c>
       <c r="E23">
-        <v>-30.79879684618279</v>
+        <v>-27.6026859325752</v>
       </c>
       <c r="F23">
-        <v>4.546392229453113</v>
+        <v>3.630112249075058</v>
       </c>
       <c r="G23">
-        <v>-5.337653313454975</v>
+        <v>-5.106454744628894</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.556835343409254</v>
       </c>
       <c r="E24">
-        <v>-31.61337875068254</v>
+        <v>-28.61508969562601</v>
       </c>
       <c r="F24">
-        <v>4.004158247007209</v>
+        <v>3.071661118055054</v>
       </c>
       <c r="G24">
-        <v>-4.920521264961267</v>
+        <v>-4.371573224730398</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.74289264245659</v>
       </c>
       <c r="E25">
-        <v>-30.414578469002</v>
+        <v>-30.23758759088621</v>
       </c>
       <c r="F25">
-        <v>4.129990016812535</v>
+        <v>2.924799317398608</v>
       </c>
       <c r="G25">
-        <v>-5.494861189478346</v>
+        <v>-6.195412352134601</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.977411677402769</v>
       </c>
       <c r="E26">
-        <v>-31.25827846137107</v>
+        <v>-28.331104562131</v>
       </c>
       <c r="F26">
-        <v>4.281987775752751</v>
+        <v>3.243559725528683</v>
       </c>
       <c r="G26">
-        <v>-5.476186402091318</v>
+        <v>-4.458491597863962</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.24732247301659</v>
       </c>
       <c r="E27">
-        <v>-32.2396395350993</v>
+        <v>-28.37181101498595</v>
       </c>
       <c r="F27">
-        <v>3.681959613334715</v>
+        <v>2.382910582842269</v>
       </c>
       <c r="G27">
-        <v>-5.060646726001998</v>
+        <v>-5.446851658067835</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.546661518420381</v>
       </c>
       <c r="E28">
-        <v>-31.3576037460183</v>
+        <v>-28.87689889190547</v>
       </c>
       <c r="F28">
-        <v>3.893580732579396</v>
+        <v>2.605448186962074</v>
       </c>
       <c r="G28">
-        <v>-4.73308810816435</v>
+        <v>-5.541791483043055</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.861075250996065</v>
       </c>
       <c r="E29">
-        <v>-31.2603660878886</v>
+        <v>-27.92866813401735</v>
       </c>
       <c r="F29">
-        <v>3.597552839159539</v>
+        <v>2.868862824465287</v>
       </c>
       <c r="G29">
-        <v>-5.612143886298107</v>
+        <v>-5.441730244118583</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.1852754895633</v>
       </c>
       <c r="E30">
-        <v>-29.97044611646273</v>
+        <v>-29.22705408760056</v>
       </c>
       <c r="F30">
-        <v>3.611848952458211</v>
+        <v>2.830996416027129</v>
       </c>
       <c r="G30">
-        <v>-5.048470539508559</v>
+        <v>-4.591949620188601</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.513086213689135</v>
       </c>
       <c r="E31">
-        <v>-30.141226192477</v>
+        <v>-28.68735508384042</v>
       </c>
       <c r="F31">
-        <v>3.468306599400526</v>
+        <v>3.125524539945065</v>
       </c>
       <c r="G31">
-        <v>-4.547671073600849</v>
+        <v>-4.89529490795202</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.83811169177863</v>
       </c>
       <c r="E32">
-        <v>-28.86576337432061</v>
+        <v>-26.91022791511431</v>
       </c>
       <c r="F32">
-        <v>3.299241241809618</v>
+        <v>2.957214610075823</v>
       </c>
       <c r="G32">
-        <v>-5.198888486630884</v>
+        <v>-4.954845001112431</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.162458963796808</v>
       </c>
       <c r="E33">
-        <v>-29.79177291025309</v>
+        <v>-27.76589213581164</v>
       </c>
       <c r="F33">
-        <v>3.111119150938228</v>
+        <v>2.248358928266534</v>
       </c>
       <c r="G33">
-        <v>-5.50497490610082</v>
+        <v>-5.008181200295629</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.479184577505788</v>
       </c>
       <c r="E34">
-        <v>-29.53249513094392</v>
+        <v>-26.23896768448332</v>
       </c>
       <c r="F34">
-        <v>3.121131339735636</v>
+        <v>2.33793650225562</v>
       </c>
       <c r="G34">
-        <v>-5.900469228949852</v>
+        <v>-5.610164180065623</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.793121177848956</v>
       </c>
       <c r="E35">
-        <v>-27.37549692008438</v>
+        <v>-26.51733751020883</v>
       </c>
       <c r="F35">
-        <v>3.231401615215854</v>
+        <v>2.352718813270332</v>
       </c>
       <c r="G35">
-        <v>-4.940215700374391</v>
+        <v>-5.571553287441103</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.100970281374605</v>
       </c>
       <c r="E36">
-        <v>-27.47392783111511</v>
+        <v>-26.51905380185774</v>
       </c>
       <c r="F36">
-        <v>3.2162867259589</v>
+        <v>2.766495241503112</v>
       </c>
       <c r="G36">
-        <v>-5.484280685934836</v>
+        <v>-5.566527879312489</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.401300962040928</v>
       </c>
       <c r="E37">
-        <v>-27.35193979829648</v>
+        <v>-26.12779817606902</v>
       </c>
       <c r="F37">
-        <v>3.233317899373536</v>
+        <v>2.347562266809661</v>
       </c>
       <c r="G37">
-        <v>-5.364630949054496</v>
+        <v>-5.320335849739048</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.695885002717675</v>
       </c>
       <c r="E38">
-        <v>-25.85368511591073</v>
+        <v>-24.58323079000683</v>
       </c>
       <c r="F38">
-        <v>3.180325515737016</v>
+        <v>2.565402599184272</v>
       </c>
       <c r="G38">
-        <v>-4.760863585238836</v>
+        <v>-5.50242909658112</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.976178774258531</v>
       </c>
       <c r="E39">
-        <v>-25.55558925740781</v>
+        <v>-24.62660451405229</v>
       </c>
       <c r="F39">
-        <v>2.972335834156438</v>
+        <v>2.335111170902476</v>
       </c>
       <c r="G39">
-        <v>-4.570798544738198</v>
+        <v>-4.533780024518068</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.244707484388811</v>
       </c>
       <c r="E40">
-        <v>-25.04268976282506</v>
+        <v>-22.78739649515503</v>
       </c>
       <c r="F40">
-        <v>3.127496253809787</v>
+        <v>2.779893393547729</v>
       </c>
       <c r="G40">
-        <v>-4.859825723044269</v>
+        <v>-4.596763153402702</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.491713078986213</v>
       </c>
       <c r="E41">
-        <v>-23.56909262141107</v>
+        <v>-24.21546888736991</v>
       </c>
       <c r="F41">
-        <v>3.440026362868523</v>
+        <v>2.431764742921745</v>
       </c>
       <c r="G41">
-        <v>-5.226779832799244</v>
+        <v>-5.593634626188042</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.716485827877547</v>
       </c>
       <c r="E42">
-        <v>-24.47031781909957</v>
+        <v>-22.59052561614557</v>
       </c>
       <c r="F42">
-        <v>3.394170158086974</v>
+        <v>2.336688541994254</v>
       </c>
       <c r="G42">
-        <v>-5.177899627911906</v>
+        <v>-4.777691088214951</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.918289052743077</v>
       </c>
       <c r="E43">
-        <v>-23.34184021028415</v>
+        <v>-21.5984003597011</v>
       </c>
       <c r="F43">
-        <v>3.278132025662726</v>
+        <v>2.53812959961449</v>
       </c>
       <c r="G43">
-        <v>-5.280996637095889</v>
+        <v>-5.632834795918551</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.091468800703663</v>
       </c>
       <c r="E44">
-        <v>-22.81381561251578</v>
+        <v>-22.18612383031259</v>
       </c>
       <c r="F44">
-        <v>3.233289392667058</v>
+        <v>2.361844126755094</v>
       </c>
       <c r="G44">
-        <v>-4.982719794553094</v>
+        <v>-6.125129470335874</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.243940365974564</v>
       </c>
       <c r="E45">
-        <v>-22.05427278110526</v>
+        <v>-20.70278594130811</v>
       </c>
       <c r="F45">
-        <v>3.106106721715862</v>
+        <v>2.389989748284284</v>
       </c>
       <c r="G45">
-        <v>-6.174754547969549</v>
+        <v>-5.995978467757826</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.369935594767757</v>
       </c>
       <c r="E46">
-        <v>-22.35862246221277</v>
+        <v>-20.2501332649234</v>
       </c>
       <c r="F46">
-        <v>3.086400669010049</v>
+        <v>2.443838916821056</v>
       </c>
       <c r="G46">
-        <v>-5.991128518542794</v>
+        <v>-5.504170443534777</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.478494517280636</v>
       </c>
       <c r="E47">
-        <v>-21.52441415136379</v>
+        <v>-20.21514627474014</v>
       </c>
       <c r="F47">
-        <v>3.197868226162339</v>
+        <v>2.029495521870549</v>
       </c>
       <c r="G47">
-        <v>-6.318260076005876</v>
+        <v>-5.869426243428107</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.571939354005917</v>
       </c>
       <c r="E48">
-        <v>-20.803680342199</v>
+        <v>-18.83848111946034</v>
       </c>
       <c r="F48">
-        <v>3.345531382011998</v>
+        <v>2.201778969881629</v>
       </c>
       <c r="G48">
-        <v>-5.853472724474359</v>
+        <v>-5.905709822538519</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.650598532656566</v>
       </c>
       <c r="E49">
-        <v>-19.87967692025192</v>
+        <v>-18.53379180280225</v>
       </c>
       <c r="F49">
-        <v>2.644643324663285</v>
+        <v>1.884817651671493</v>
       </c>
       <c r="G49">
-        <v>-6.517025230183719</v>
+        <v>-4.931638076882139</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.725159597799158</v>
       </c>
       <c r="E50">
-        <v>-18.39810966458443</v>
+        <v>-17.9994046990531</v>
       </c>
       <c r="F50">
-        <v>3.032180913289064</v>
+        <v>1.702167264737946</v>
       </c>
       <c r="G50">
-        <v>-6.412716561332362</v>
+        <v>-6.704918552810594</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.790067970753102</v>
       </c>
       <c r="E51">
-        <v>-18.89693466195135</v>
+        <v>-18.94015894635456</v>
       </c>
       <c r="F51">
-        <v>3.016730278378037</v>
+        <v>1.572735731386827</v>
       </c>
       <c r="G51">
-        <v>-6.355222316951839</v>
+        <v>-5.455114779733857</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.85521389463397</v>
       </c>
       <c r="E52">
-        <v>-18.25157730264423</v>
+        <v>-17.09244192479688</v>
       </c>
       <c r="F52">
-        <v>2.814804606747677</v>
+        <v>2.515414505669342</v>
       </c>
       <c r="G52">
-        <v>-6.347624614939211</v>
+        <v>-5.60649609560811</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.915934012638426</v>
       </c>
       <c r="E53">
-        <v>-18.9182818884235</v>
+        <v>-17.38542513614514</v>
       </c>
       <c r="F53">
-        <v>2.781611714465981</v>
+        <v>2.229500158225481</v>
       </c>
       <c r="G53">
-        <v>-6.453522345649418</v>
+        <v>-5.707530634921127</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.973525125455949</v>
       </c>
       <c r="E54">
-        <v>-17.00018332383862</v>
+        <v>-17.17142303996466</v>
       </c>
       <c r="F54">
-        <v>2.570742855531134</v>
+        <v>2.403416407035379</v>
       </c>
       <c r="G54">
-        <v>-6.958555999301856</v>
+        <v>-6.783941274832997</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.032648001065132</v>
       </c>
       <c r="E55">
-        <v>-17.20260158350747</v>
+        <v>-15.57961008458044</v>
       </c>
       <c r="F55">
-        <v>2.686578273598206</v>
+        <v>1.989160115910221</v>
       </c>
       <c r="G55">
-        <v>-7.448218790015457</v>
+        <v>-6.396316118730812</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.085906910265441</v>
       </c>
       <c r="E56">
-        <v>-16.18518479973017</v>
+        <v>-14.95270625685458</v>
       </c>
       <c r="F56">
-        <v>2.667032175189853</v>
+        <v>2.330664124691922</v>
       </c>
       <c r="G56">
-        <v>-7.113992733461717</v>
+        <v>-6.171973689716561</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.143923482687248</v>
       </c>
       <c r="E57">
-        <v>-16.65592872977551</v>
+        <v>-16.01141366663383</v>
       </c>
       <c r="F57">
-        <v>3.078741867202984</v>
+        <v>1.962195938993949</v>
       </c>
       <c r="G57">
-        <v>-6.617285101840547</v>
+        <v>-6.846917782626552</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.198997869705638</v>
       </c>
       <c r="E58">
-        <v>-15.8767866628598</v>
+        <v>-14.77740449954366</v>
       </c>
       <c r="F58">
-        <v>2.746706836089696</v>
+        <v>2.383137052788177</v>
       </c>
       <c r="G58">
-        <v>-7.908252198152582</v>
+        <v>-6.815891349832503</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.259924094611401</v>
       </c>
       <c r="E59">
-        <v>-15.75986146398175</v>
+        <v>-13.64517731424989</v>
       </c>
       <c r="F59">
-        <v>2.613078482062662</v>
+        <v>2.270882393795914</v>
       </c>
       <c r="G59">
-        <v>-7.15753633893975</v>
+        <v>-7.112711552338019</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.329198262707671</v>
       </c>
       <c r="E60">
-        <v>-16.43221305684858</v>
+        <v>-13.75362973825958</v>
       </c>
       <c r="F60">
-        <v>2.115959530029881</v>
+        <v>1.958911332925328</v>
       </c>
       <c r="G60">
-        <v>-7.0901766688522</v>
+        <v>-7.720123826792418</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.404450872451871</v>
       </c>
       <c r="E61">
-        <v>-14.98963596238714</v>
+        <v>-14.05058894978657</v>
       </c>
       <c r="F61">
-        <v>2.570137879871436</v>
+        <v>2.033719265547026</v>
       </c>
       <c r="G61">
-        <v>-7.398729444748892</v>
+        <v>-7.566832326142005</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.497872583691564</v>
       </c>
       <c r="E62">
-        <v>-15.86801048023293</v>
+        <v>-13.73620417027807</v>
       </c>
       <c r="F62">
-        <v>2.458014668470154</v>
+        <v>2.016987412550408</v>
       </c>
       <c r="G62">
-        <v>-7.657749838287009</v>
+        <v>-7.426408916002738</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.600838814908759</v>
       </c>
       <c r="E63">
-        <v>-14.72308092534765</v>
+        <v>-12.25158925160342</v>
       </c>
       <c r="F63">
-        <v>2.44409072606161</v>
+        <v>2.058607204008156</v>
       </c>
       <c r="G63">
-        <v>-7.840511815328014</v>
+        <v>-6.968490946465209</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.723860545365218</v>
       </c>
       <c r="E64">
-        <v>-14.54160232949025</v>
+        <v>-12.61347319497838</v>
       </c>
       <c r="F64">
-        <v>2.137547025363236</v>
+        <v>1.963006796422654</v>
       </c>
       <c r="G64">
-        <v>-8.051903390192637</v>
+        <v>-6.95971800078614</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.860840268998775</v>
       </c>
       <c r="E65">
-        <v>-14.46591794340006</v>
+        <v>-12.26580413151349</v>
       </c>
       <c r="F65">
-        <v>2.595028985744398</v>
+        <v>2.055515810061219</v>
       </c>
       <c r="G65">
-        <v>-7.245133373908866</v>
+        <v>-6.979819633300594</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.01027831881348</v>
       </c>
       <c r="E66">
-        <v>-14.51331748083835</v>
+        <v>-13.30546930809049</v>
       </c>
       <c r="F66">
-        <v>1.980929596267683</v>
+        <v>2.022492374312475</v>
       </c>
       <c r="G66">
-        <v>-7.884747324823755</v>
+        <v>-7.223614827903603</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.17546582447852</v>
       </c>
       <c r="E67">
-        <v>-14.75726184715754</v>
+        <v>-12.53712312320905</v>
       </c>
       <c r="F67">
-        <v>2.452235725584716</v>
+        <v>1.560758163548358</v>
       </c>
       <c r="G67">
-        <v>-8.124195773133701</v>
+        <v>-7.566593966863177</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.343160400274098</v>
       </c>
       <c r="E68">
-        <v>-13.14951772021433</v>
+        <v>-11.77010830968588</v>
       </c>
       <c r="F68">
-        <v>2.23674086167087</v>
+        <v>1.534200999052354</v>
       </c>
       <c r="G68">
-        <v>-8.095427132397434</v>
+        <v>-8.170497063045948</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.518927408677653</v>
       </c>
       <c r="E69">
-        <v>-13.6398699427129</v>
+        <v>-11.93060648546573</v>
       </c>
       <c r="F69">
-        <v>2.114417000468243</v>
+        <v>1.694700091346649</v>
       </c>
       <c r="G69">
-        <v>-7.829010980124586</v>
+        <v>-8.17485374097563</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.685905950249836</v>
       </c>
       <c r="E70">
-        <v>-14.34390273973739</v>
+        <v>-12.65551554766559</v>
       </c>
       <c r="F70">
-        <v>2.236253080248915</v>
+        <v>1.368513686179079</v>
       </c>
       <c r="G70">
-        <v>-8.473802624262897</v>
+        <v>-7.570149492772354</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.843425527725088</v>
       </c>
       <c r="E71">
-        <v>-14.4268598550839</v>
+        <v>-13.54623468565629</v>
       </c>
       <c r="F71">
-        <v>1.96506403040681</v>
+        <v>1.576878706061616</v>
       </c>
       <c r="G71">
-        <v>-7.764243467194285</v>
+        <v>-7.964660583596223</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.984145633521058</v>
       </c>
       <c r="E72">
-        <v>-14.60578439160097</v>
+        <v>-11.8257315559221</v>
       </c>
       <c r="F72">
-        <v>2.177329717959075</v>
+        <v>0.9326873204856359</v>
       </c>
       <c r="G72">
-        <v>-7.974790852946393</v>
+        <v>-7.190045896135394</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.09359309154222</v>
       </c>
       <c r="E73">
-        <v>-13.71157380015035</v>
+        <v>-12.05007668673609</v>
       </c>
       <c r="F73">
-        <v>2.111111806222721</v>
+        <v>1.10565017833444</v>
       </c>
       <c r="G73">
-        <v>-8.080913700753269</v>
+        <v>-7.056137639617413</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.17372158068457</v>
       </c>
       <c r="E74">
-        <v>-14.13922930001271</v>
+        <v>-13.75044169255818</v>
       </c>
       <c r="F74">
-        <v>1.974773731374369</v>
+        <v>1.427145646580478</v>
       </c>
       <c r="G74">
-        <v>-8.480215150972464</v>
+        <v>-8.270359669238063</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.20741199628239</v>
       </c>
       <c r="E75">
-        <v>-14.68955210379485</v>
+        <v>-12.57904320709806</v>
       </c>
       <c r="F75">
-        <v>1.81359206183052</v>
+        <v>1.236565644128326</v>
       </c>
       <c r="G75">
-        <v>-7.051827309325282</v>
+        <v>-7.632043452174568</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.19662807238663</v>
       </c>
       <c r="E76">
-        <v>-14.80173146191286</v>
+        <v>-13.92707482122736</v>
       </c>
       <c r="F76">
-        <v>1.534373622997137</v>
+        <v>1.222899845783999</v>
       </c>
       <c r="G76">
-        <v>-6.602152598180537</v>
+        <v>-7.660156604894059</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.13350510365345</v>
       </c>
       <c r="E77">
-        <v>-16.2804910636956</v>
+        <v>-14.33752211986058</v>
       </c>
       <c r="F77">
-        <v>1.707954126152962</v>
+        <v>1.585785468130048</v>
       </c>
       <c r="G77">
-        <v>-7.271932240049266</v>
+        <v>-7.83312929877544</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.01341869778514</v>
       </c>
       <c r="E78">
-        <v>-15.07606188882353</v>
+        <v>-14.91691319829796</v>
       </c>
       <c r="F78">
-        <v>1.794443473606941</v>
+        <v>1.329742981663206</v>
       </c>
       <c r="G78">
-        <v>-6.197206667816886</v>
+        <v>-7.875537387133503</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.844104703039765</v>
       </c>
       <c r="E79">
-        <v>-15.53675713504586</v>
+        <v>-13.74938202964039</v>
       </c>
       <c r="F79">
-        <v>1.830661244187126</v>
+        <v>1.184414208332905</v>
       </c>
       <c r="G79">
-        <v>-7.349458595487919</v>
+        <v>-7.020370505611127</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.619643800623759</v>
       </c>
       <c r="E80">
-        <v>-17.13961956700879</v>
+        <v>-13.93631743667702</v>
       </c>
       <c r="F80">
-        <v>1.45255779169962</v>
+        <v>1.200691537731792</v>
       </c>
       <c r="G80">
-        <v>-6.78896668296161</v>
+        <v>-6.724927490049949</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.355601385328688</v>
       </c>
       <c r="E81">
-        <v>-16.99242151938947</v>
+        <v>-15.62055201808379</v>
       </c>
       <c r="F81">
-        <v>1.460452565688085</v>
+        <v>0.876475262723028</v>
       </c>
       <c r="G81">
-        <v>-6.309242149956901</v>
+        <v>-7.933452070797514</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.052857199064981</v>
       </c>
       <c r="E82">
-        <v>-17.27444129516515</v>
+        <v>-16.34734492547083</v>
       </c>
       <c r="F82">
-        <v>1.54402631055174</v>
+        <v>0.9768125347016097</v>
       </c>
       <c r="G82">
-        <v>-6.224839791433182</v>
+        <v>-6.965796162396241</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.725233194093079</v>
       </c>
       <c r="E83">
-        <v>-17.59334549173332</v>
+        <v>-17.96532340367137</v>
       </c>
       <c r="F83">
-        <v>1.676636341675147</v>
+        <v>0.981538313153281</v>
       </c>
       <c r="G83">
-        <v>-6.292182908793037</v>
+        <v>-5.9572152900385</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.387287448856247</v>
       </c>
       <c r="E84">
-        <v>-18.62256347877461</v>
+        <v>-17.39961737368518</v>
       </c>
       <c r="F84">
-        <v>1.676941996916827</v>
+        <v>0.7368636677474636</v>
       </c>
       <c r="G84">
-        <v>-5.87054520782038</v>
+        <v>-6.420843950631273</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.043932970981745</v>
       </c>
       <c r="E85">
-        <v>-19.70144071178402</v>
+        <v>-18.65670364431844</v>
       </c>
       <c r="F85">
-        <v>1.138765469026279</v>
+        <v>0.9588390562672874</v>
       </c>
       <c r="G85">
-        <v>-5.98610311041418</v>
+        <v>-6.626812851902568</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.718582736831934</v>
       </c>
       <c r="E86">
-        <v>-20.48373006813507</v>
+        <v>-19.15864876027664</v>
       </c>
       <c r="F86">
-        <v>1.383566810905331</v>
+        <v>0.7869135257930965</v>
       </c>
       <c r="G86">
-        <v>-5.4257568618916</v>
+        <v>-5.096086115999896</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.414483041791708</v>
       </c>
       <c r="E87">
-        <v>-21.84335910419802</v>
+        <v>-20.82473321786066</v>
       </c>
       <c r="F87">
-        <v>1.136092173441017</v>
+        <v>0.6525550833390446</v>
       </c>
       <c r="G87">
-        <v>-5.13904375491748</v>
+        <v>-5.848404279253734</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.150797105376792</v>
       </c>
       <c r="E88">
-        <v>-22.43686090764329</v>
+        <v>-21.98361952963759</v>
       </c>
       <c r="F88">
-        <v>1.542756178407558</v>
+        <v>0.716935896213489</v>
       </c>
       <c r="G88">
-        <v>-4.280241894392984</v>
+        <v>-5.310304896755056</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.935583756029366</v>
       </c>
       <c r="E89">
-        <v>-24.89826314129843</v>
+        <v>-24.56267604648601</v>
       </c>
       <c r="F89">
-        <v>1.22618128444079</v>
+        <v>0.3968887270271197</v>
       </c>
       <c r="G89">
-        <v>-4.267562504977575</v>
+        <v>-5.140977113512414</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.773333290972236</v>
       </c>
       <c r="E90">
-        <v>-25.50393295440232</v>
+        <v>-23.90184489149469</v>
       </c>
       <c r="F90">
-        <v>1.149485574367888</v>
+        <v>0.6015850921565414</v>
       </c>
       <c r="G90">
-        <v>-4.298668390864567</v>
+        <v>-5.215424661599545</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.678193189611796</v>
       </c>
       <c r="E91">
-        <v>-27.98388381759288</v>
+        <v>-27.36030841826266</v>
       </c>
       <c r="F91">
-        <v>1.051981552272028</v>
+        <v>0.5087379573050307</v>
       </c>
       <c r="G91">
-        <v>-4.813004677482357</v>
+        <v>-5.148677442436759</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.642629711763793</v>
       </c>
       <c r="E92">
-        <v>-29.05879410737156</v>
+        <v>-28.2094244655449</v>
       </c>
       <c r="F92">
-        <v>0.9485101262867913</v>
+        <v>-0.005705945589699981</v>
       </c>
       <c r="G92">
-        <v>-4.800692758621807</v>
+        <v>-5.29071308825365</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.676007487407582</v>
       </c>
       <c r="E93">
-        <v>-31.29801129231436</v>
+        <v>-29.82445490716644</v>
       </c>
       <c r="F93">
-        <v>0.5787702247387208</v>
+        <v>0.1283096245336592</v>
       </c>
       <c r="G93">
-        <v>-4.837158417736879</v>
+        <v>-5.831023915172561</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.76475385440659</v>
       </c>
       <c r="E94">
-        <v>-32.82835474151847</v>
+        <v>-31.64441917576811</v>
       </c>
       <c r="F94">
-        <v>0.3274067973990448</v>
+        <v>-0.1996639927594845</v>
       </c>
       <c r="G94">
-        <v>-5.171573175386358</v>
+        <v>-5.779217188028506</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.905453254749212</v>
       </c>
       <c r="E95">
-        <v>-34.8405255609017</v>
+        <v>-33.27301692551664</v>
       </c>
       <c r="F95">
-        <v>0.4665646606298359</v>
+        <v>-0.2023119490500993</v>
       </c>
       <c r="G95">
-        <v>-5.281009879278046</v>
+        <v>-6.055406070733283</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.093964443288836</v>
       </c>
       <c r="E96">
-        <v>-37.66140032552271</v>
+        <v>-37.45023305407103</v>
       </c>
       <c r="F96">
-        <v>0.2564765687113005</v>
+        <v>-0.5104472741934908</v>
       </c>
       <c r="G96">
-        <v>-5.143595755033977</v>
+        <v>-4.882337432711313</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.312215018819788</v>
       </c>
       <c r="E97">
-        <v>-39.18517295894168</v>
+        <v>-37.48397697813919</v>
       </c>
       <c r="F97">
-        <v>-0.09004937152825863</v>
+        <v>-0.02753258051628645</v>
       </c>
       <c r="G97">
-        <v>-5.810683923379279</v>
+        <v>-7.046772106286815</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.569931843236627</v>
       </c>
       <c r="E98">
-        <v>-41.75230373949091</v>
+        <v>-39.0991025177149</v>
       </c>
       <c r="F98">
-        <v>-0.1766883791912468</v>
+        <v>-0.7476420765606877</v>
       </c>
       <c r="G98">
-        <v>-6.275603696732367</v>
+        <v>-6.544519310887366</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.841429534047969</v>
       </c>
       <c r="E99">
-        <v>-43.93520935014833</v>
+        <v>-41.95066448644889</v>
       </c>
       <c r="F99">
-        <v>-0.4167940330310214</v>
+        <v>-0.7717563746821265</v>
       </c>
       <c r="G99">
-        <v>-6.592436147022776</v>
+        <v>-6.774512841137152</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.146276733383104</v>
       </c>
       <c r="E100">
-        <v>-46.16275439333636</v>
+        <v>-45.01165252837862</v>
       </c>
       <c r="F100">
-        <v>-0.5704047964461129</v>
+        <v>-0.9481479558378567</v>
       </c>
       <c r="G100">
-        <v>-5.944658390808044</v>
+        <v>-6.138610011771786</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.450834468459721</v>
       </c>
       <c r="E101">
-        <v>-47.2084107410255</v>
+        <v>-47.26340679361165</v>
       </c>
       <c r="F101">
-        <v>-0.6609595169850251</v>
+        <v>-1.528443934402475</v>
       </c>
       <c r="G101">
-        <v>-6.508993846705446</v>
+        <v>-6.2193111803826</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.795827256399217</v>
       </c>
       <c r="E102">
-        <v>-49.68351274067234</v>
+        <v>-49.05644702000071</v>
       </c>
       <c r="F102">
-        <v>-1.112594435126385</v>
+        <v>-1.799492826271063</v>
       </c>
       <c r="G102">
-        <v>-6.141016778378837</v>
+        <v>-7.332048436496891</v>
       </c>
     </row>
   </sheetData>
